--- a/GBR_WB_timeseries.xlsx
+++ b/GBR_WB_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Control of Corruption</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t>Foreign direct investment, net outflows (BoP, current US$)</t>
+  </si>
+  <si>
+    <t>GDP (current US$)</t>
   </si>
   <si>
     <t>GDP growth (annual %)</t>
@@ -440,12 +443,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W36"/>
+  <dimension ref="A1:X36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -513,8 +516,11 @@
       <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:23">
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
       <c r="A2" s="1">
         <v>1990</v>
       </c>
@@ -534,49 +540,52 @@
         <v>27983492260.7354</v>
       </c>
       <c r="H2">
+        <v>1093169389204.55</v>
+      </c>
+      <c r="I2">
         <v>0.733755470094508</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>19095.4669984608</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>35.7</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>18.5427637723272</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>32.583043271347</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>32.6096807883406</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>24.9113763312668</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>8.06346090938832</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>9.0097455198026</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>-0.90941132711683</v>
       </c>
-      <c r="S2">
+      <c r="T2">
         <v>24.1512945995683</v>
       </c>
-      <c r="T2">
+      <c r="U2">
         <v>43145747847.3062</v>
       </c>
-      <c r="U2">
+      <c r="V2">
         <v>1.26564143976707</v>
       </c>
-      <c r="V2">
+      <c r="W2">
         <v>48.2329411879358</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:24">
       <c r="A3" s="1">
         <v>1991</v>
       </c>
@@ -596,52 +605,55 @@
         <v>23546604903.818</v>
       </c>
       <c r="H3">
+        <v>1142797178130.51</v>
+      </c>
+      <c r="I3">
         <v>-1.10312166586773</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>19900.7266505069</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>35</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>19.3976855267097</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>34.7840781769414</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>33.01500387366</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>22.712070077751</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>7.46178295746934</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>7.26211128315934</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>-2.33469040042224</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>24.847137041141</v>
       </c>
-      <c r="T3">
+      <c r="U3">
         <v>48572195808.5626</v>
       </c>
-      <c r="U3">
+      <c r="V3">
         <v>1.49335400907614</v>
       </c>
-      <c r="V3">
+      <c r="W3">
         <v>45.2998069343145</v>
       </c>
-      <c r="W3">
+      <c r="X3">
         <v>8.550000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:24">
       <c r="A4" s="1">
         <v>1992</v>
       </c>
@@ -661,52 +673,55 @@
         <v>26150828653.9306</v>
       </c>
       <c r="H4">
+        <v>1179659529659.53</v>
+      </c>
+      <c r="I4">
         <v>0.401082085841935</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>20487.1707852878</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>35</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>19.8755904012378</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>37.6406266271925</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>32.4523558028475</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>23.3741489504143</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>4.5915492957746</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>6.61201775430913</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>-6.1029203921627</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>24.2803159914902</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>42844142573.8515</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>1.33812693071793</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <v>46.2897460463871</v>
       </c>
-      <c r="W4">
+      <c r="X4">
         <v>9.772</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:24">
       <c r="A5" s="1">
         <v>1993</v>
       </c>
@@ -726,52 +741,55 @@
         <v>30421803356.97</v>
       </c>
       <c r="H5">
+        <v>1061388722255.55</v>
+      </c>
+      <c r="I5">
         <v>2.48983092921434</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>18389.0195675099</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>35.1</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>19.1850113178115</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>37.368983262073</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>30.5948280003504</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>24.9074525174713</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>2.55857796929706</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>6.95156027269324</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>-7.48586333283409</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>22.9810917661155</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>43982206193.9429</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>1.44625371820275</v>
       </c>
-      <c r="V5">
+      <c r="W5">
         <v>49.7307933489136</v>
       </c>
-      <c r="W5">
+      <c r="X5">
         <v>10.346</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:24">
       <c r="A6" s="1">
         <v>1994</v>
       </c>
@@ -791,52 +809,55 @@
         <v>43732748607.769</v>
       </c>
       <c r="H6">
+        <v>1140489745944.29</v>
+      </c>
+      <c r="I6">
         <v>3.84600918007958</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>19709.2380983653</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>36</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>18.8330325176195</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>37.079774985373</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>31.6075233898196</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>25.7991054702387</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>2.21901260504204</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>7.78417542170768</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>-6.20185830305047</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <v>23.7970949924584</v>
       </c>
-      <c r="T6">
+      <c r="U6">
         <v>48079032624.0768</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>1.46821849351434</v>
       </c>
-      <c r="V6">
+      <c r="W6">
         <v>51.8679570207033</v>
       </c>
-      <c r="W6">
+      <c r="X6">
         <v>9.648</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:24">
       <c r="A7" s="1">
         <v>1995</v>
       </c>
@@ -856,52 +877,55 @@
         <v>56508877717.1525</v>
       </c>
       <c r="H7">
+        <v>1344240176739.78</v>
+      </c>
+      <c r="I7">
         <v>2.53167000543779</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>23168.9529580171</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>35.5</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>17.0415979432878</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>37.1148507064079</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>30.481249523094</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>25.215150643603</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>2.69749518304432</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>8.261297250451509</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>-7.03097394479042</v>
       </c>
-      <c r="S7">
+      <c r="T7">
         <v>23.2315738191807</v>
       </c>
-      <c r="T7">
+      <c r="U7">
         <v>49144184297.8559</v>
       </c>
-      <c r="U7">
+      <c r="V7">
         <v>1.27485538720077</v>
       </c>
-      <c r="V7">
+      <c r="W7">
         <v>50.9957797486632</v>
       </c>
-      <c r="W7">
+      <c r="X7">
         <v>8.694000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:24">
       <c r="A8" s="1">
         <v>1996</v>
       </c>
@@ -924,55 +948,58 @@
         <v>41714201072.5659</v>
       </c>
       <c r="H8">
+        <v>1419645865834.63</v>
+      </c>
+      <c r="I8">
         <v>2.58199387517438</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>24406.400298359</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>35.3</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>16.601226602842</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>35.8625835583351</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>30.2178148623121</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>25.882616679469</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>2.85178236397749</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>8.508734567806661</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>-5.88037490398278</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>0.981364369392395</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <v>23.0650125880089</v>
       </c>
-      <c r="T8">
+      <c r="U8">
         <v>46700021359.8396</v>
       </c>
-      <c r="U8">
+      <c r="V8">
         <v>1.12325191665556</v>
       </c>
-      <c r="V8">
+      <c r="W8">
         <v>52.2438084688564</v>
       </c>
-      <c r="W8">
+      <c r="X8">
         <v>8.189</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:24">
       <c r="A9" s="1">
         <v>1997</v>
       </c>
@@ -992,52 +1019,55 @@
         <v>74698652866.2142</v>
       </c>
       <c r="H9">
+        <v>1560911918795.02</v>
+      </c>
+      <c r="I9">
         <v>4.92464829983174</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>26766.0056249684</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>35.7</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>16.0427100759908</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>34.4814638060425</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>30.8504780235052</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>25.2043989700075</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>2.20114313510882</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>9.068952510737709</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>-3.8503049595922</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <v>23.7371316491942</v>
       </c>
-      <c r="T9">
+      <c r="U9">
         <v>37662299516.2776</v>
       </c>
-      <c r="U9">
+      <c r="V9">
         <v>0.848240799085382</v>
       </c>
-      <c r="V9">
+      <c r="W9">
         <v>50.9734058453648</v>
       </c>
-      <c r="W9">
+      <c r="X9">
         <v>7.072</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:24">
       <c r="A10" s="1">
         <v>1998</v>
       </c>
@@ -1060,55 +1090,58 @@
         <v>157974733405.176</v>
       </c>
       <c r="H10">
+        <v>1653694932096.72</v>
+      </c>
+      <c r="I10">
         <v>3.40265822823224</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>28274.5045119699</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>36.6</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>16.0397435756199</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>34.0053740557095</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>32.0474391112277</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>24.9068353461839</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>1.82056163731556</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>9.04006549961124</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <v>-2.19659269244598</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <v>0.930068552494049</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>25.0251126438531</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <v>38829795838.1208</v>
       </c>
-      <c r="U10">
+      <c r="V10">
         <v>0.849729315522173</v>
       </c>
-      <c r="V10">
+      <c r="W10">
         <v>49.3364553465645</v>
       </c>
-      <c r="W10">
+      <c r="X10">
         <v>6.198</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:24">
       <c r="A11" s="1">
         <v>1999</v>
       </c>
@@ -1128,52 +1161,55 @@
         <v>242345729902.125</v>
       </c>
       <c r="H11">
+        <v>1687830448147.55</v>
+      </c>
+      <c r="I11">
         <v>3.05832327041962</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>28762.0913570256</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>36.8</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>16.4530389705995</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>33.6684086621781</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>32.4188495928101</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>25.3260969587289</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>1.7529508005142</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>7.70174664408034</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>-1.39765424903762</v>
       </c>
-      <c r="S11">
+      <c r="T11">
         <v>25.4816687882459</v>
       </c>
-      <c r="T11">
+      <c r="U11">
         <v>46188288221.5174</v>
       </c>
-      <c r="U11">
+      <c r="V11">
         <v>0.90959988381713</v>
       </c>
-      <c r="V11">
+      <c r="W11">
         <v>49.6314395043173</v>
       </c>
-      <c r="W11">
+      <c r="X11">
         <v>6.042</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:24">
       <c r="A12" s="1">
         <v>2000</v>
       </c>
@@ -1196,55 +1232,58 @@
         <v>292046714700.285</v>
       </c>
       <c r="H12">
+        <v>1665534876683.31</v>
+      </c>
+      <c r="I12">
         <v>4.34163419265596</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>28280.926786099</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>38.8</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>16.6408964053665</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>34.096871956626</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>33.0191541782345</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>26.8619089495181</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>1.18295624210409</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>7.22659476396268</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>-0.788006744480137</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>1.03310573101044</v>
       </c>
-      <c r="S12">
+      <c r="T12">
         <v>26.089164498452</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <v>50939389681.351</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <v>0.935057175777233</v>
       </c>
-      <c r="V12">
+      <c r="W12">
         <v>52.521730598718</v>
       </c>
-      <c r="W12">
+      <c r="X12">
         <v>5.558</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:24">
       <c r="A13" s="1">
         <v>2001</v>
       </c>
@@ -1264,52 +1303,55 @@
         <v>77411943366.3992</v>
       </c>
       <c r="H13">
+        <v>1649827263567.01</v>
+      </c>
+      <c r="I13">
         <v>2.57278043964686</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>27906.5695029641</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>37.1</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>17.2634986279976</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>34.392458131023</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>32.7263367753362</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>27.2744484724749</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>1.53234960272418</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>6.26281127595235</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>-1.86217155919678</v>
       </c>
-      <c r="S13">
+      <c r="T13">
         <v>25.7422554934628</v>
       </c>
-      <c r="T13">
+      <c r="U13">
         <v>47417467709.4427</v>
       </c>
-      <c r="U13">
+      <c r="V13">
         <v>0.876404449269559</v>
       </c>
-      <c r="V13">
+      <c r="W13">
         <v>52.8216135097523</v>
       </c>
-      <c r="W13">
+      <c r="X13">
         <v>4.696</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:24">
       <c r="A14" s="1">
         <v>2002</v>
       </c>
@@ -1332,55 +1374,58 @@
         <v>120902004481.173</v>
       </c>
       <c r="H14">
+        <v>1785729916067.15</v>
+      </c>
+      <c r="I14">
         <v>1.79566074059649</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>30077.741432188</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>35.1</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>18.1387381141628</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>35.7521450951329</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>31.6339317413649</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>26.8692732066014</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>1.52040245947455</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>5.28658457854519</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>-4.32611321267811</v>
       </c>
-      <c r="R14">
+      <c r="S14">
         <v>0.672591328620911</v>
       </c>
-      <c r="S14">
+      <c r="T14">
         <v>24.9615800725006</v>
       </c>
-      <c r="T14">
+      <c r="U14">
         <v>54959281998.9798</v>
       </c>
-      <c r="U14">
+      <c r="V14">
         <v>1.00793032280885</v>
       </c>
-      <c r="V14">
+      <c r="W14">
         <v>51.3796342070387</v>
       </c>
-      <c r="W14">
+      <c r="X14">
         <v>5.037</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:24">
       <c r="A15" s="1">
         <v>2003</v>
       </c>
@@ -1403,55 +1448,58 @@
         <v>82080876360.4201</v>
       </c>
       <c r="H15">
+        <v>2054422857142.86</v>
+      </c>
+      <c r="I15">
         <v>3.15234651882265</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>34442.6875402308</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>34.9</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>18.8381622049472</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>36.9533049254014</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>31.4074800490172</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>26.1830324858106</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>1.37650038542013</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>5.09015131312958</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>-5.76015588865913</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <v>0.27125072479248</v>
       </c>
-      <c r="S15">
+      <c r="T15">
         <v>24.5554042090574</v>
       </c>
-      <c r="T15">
+      <c r="U15">
         <v>56349681040.0796</v>
       </c>
-      <c r="U15">
+      <c r="V15">
         <v>0.9245702466754639</v>
       </c>
-      <c r="V15">
+      <c r="W15">
         <v>50.2395230519083</v>
       </c>
-      <c r="W15">
+      <c r="X15">
         <v>4.807</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:24">
       <c r="A16" s="1">
         <v>2004</v>
       </c>
@@ -1474,55 +1522,58 @@
         <v>128639685536.356</v>
       </c>
       <c r="H16">
+        <v>2421525082387.4</v>
+      </c>
+      <c r="I16">
         <v>2.45790443810543</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>40366.8886650968</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>34.8</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>19.4000319059576</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>37.4139692145313</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>32.5266872165227</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>26.3794223207123</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>1.39039756680422</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>5.1395268474753</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>-5.52343537947298</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <v>0.140847533941269</v>
       </c>
-      <c r="S16">
+      <c r="T16">
         <v>25.1523282654273</v>
       </c>
-      <c r="T16">
+      <c r="U16">
         <v>62138194998.7523</v>
       </c>
-      <c r="U16">
+      <c r="V16">
         <v>0.837146297763696</v>
       </c>
-      <c r="V16">
+      <c r="W16">
         <v>50.4517112404991</v>
       </c>
-      <c r="W16">
+      <c r="X16">
         <v>4.594</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:24">
       <c r="A17" s="1">
         <v>2005</v>
       </c>
@@ -1545,55 +1596,58 @@
         <v>159910443047.888</v>
       </c>
       <c r="H17">
+        <v>2543180000000</v>
+      </c>
+      <c r="I17">
         <v>2.73266076681189</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>42104.7884375024</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>35.5</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>19.5974402841396</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>37.8516088304621</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>33.5427585649748</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>27.4092063694058</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>2.0891364902507</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>5.39844253176415</v>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <v>-5.41869913758651</v>
       </c>
-      <c r="R17">
+      <c r="S17">
         <v>0.124187760055065</v>
       </c>
-      <c r="S17">
+      <c r="T17">
         <v>25.488132609925</v>
       </c>
-      <c r="T17">
+      <c r="U17">
         <v>59135108205.007</v>
       </c>
-      <c r="U17">
+      <c r="V17">
         <v>0.686589142942834</v>
       </c>
-      <c r="V17">
+      <c r="W17">
         <v>52.6807168405482</v>
       </c>
-      <c r="W17">
+      <c r="X17">
         <v>4.835</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:24">
       <c r="A18" s="1">
         <v>2006</v>
       </c>
@@ -1616,55 +1670,58 @@
         <v>142254950302.494</v>
       </c>
       <c r="H18">
+        <v>2708441582336.71</v>
+      </c>
+      <c r="I18">
         <v>2.38069403532468</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>44512.4590296865</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>35.9</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>19.7937824974627</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>38.1085270896539</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>33.3884723084594</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>29.4022980385017</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>2.45566166439291</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>5.39955648410259</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <v>-5.34306858926196</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <v>0.667080104351044</v>
       </c>
-      <c r="S18">
+      <c r="T18">
         <v>25.770394514272</v>
       </c>
-      <c r="T18">
+      <c r="U18">
         <v>63823577313.6433</v>
       </c>
-      <c r="U18">
+      <c r="V18">
         <v>0.597484134087491</v>
       </c>
-      <c r="V18">
+      <c r="W18">
         <v>56.9144274808123</v>
       </c>
-      <c r="W18">
+      <c r="X18">
         <v>5.411</v>
       </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:24">
       <c r="A19" s="1">
         <v>2007</v>
       </c>
@@ -1687,55 +1744,58 @@
         <v>370395276356.724</v>
       </c>
       <c r="H19">
+        <v>3090510204081.63</v>
+      </c>
+      <c r="I19">
         <v>2.62487995340285</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>50397.6854954706</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>34.4</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>19.6826827273981</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>38.4127144435877</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>33.7206087902854</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>27.4527931157936</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>2.38656150773327</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>5.9017051018224</v>
       </c>
-      <c r="Q19">
+      <c r="R19">
         <v>-5.20057463339283</v>
       </c>
-      <c r="R19">
+      <c r="S19">
         <v>0.574654936790466</v>
       </c>
-      <c r="S19">
+      <c r="T19">
         <v>25.9947159105991</v>
       </c>
-      <c r="T19">
+      <c r="U19">
         <v>77715465906.56619</v>
       </c>
-      <c r="U19">
+      <c r="V19">
         <v>0.614730670256313</v>
       </c>
-      <c r="V19">
+      <c r="W19">
         <v>52.9643534370859</v>
       </c>
-      <c r="W19">
+      <c r="X19">
         <v>5.342</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:24">
       <c r="A20" s="1">
         <v>2008</v>
       </c>
@@ -1758,55 +1818,58 @@
         <v>356696266893.072</v>
       </c>
       <c r="H20">
+        <v>2929411764705.88</v>
+      </c>
+      <c r="I20">
         <v>-0.248797260756646</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>47396.1202078484</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>35.4</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>20.3799573293173</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>41.2181852409639</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>34.4186119477912</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>29.1926455823293</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>3.52140856342538</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>5.52208789485623</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>-7.65775602409638</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <v>0.492879867553711</v>
       </c>
-      <c r="S20">
+      <c r="T20">
         <v>26.4580823293173</v>
       </c>
-      <c r="T20">
+      <c r="U20">
         <v>64785716443.2505</v>
       </c>
-      <c r="U20">
+      <c r="V20">
         <v>0.530752979118063</v>
       </c>
-      <c r="V20">
+      <c r="W20">
         <v>56.6986069277108</v>
       </c>
-      <c r="W20">
+      <c r="X20">
         <v>5.705</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:24">
       <c r="A21" s="1">
         <v>2009</v>
       </c>
@@ -1829,55 +1892,58 @@
         <v>-48397913516.0543</v>
       </c>
       <c r="H21">
+        <v>2412840006231.5</v>
+      </c>
+      <c r="I21">
         <v>-4.62055370768425</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>38744.131693043</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>35.1</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>21.9893181956118</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>43.7888122561825</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>32.1307694592337</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>28.12283300254</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>1.9617317356011</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>4.57592280765907</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>-12.5247126488731</v>
       </c>
-      <c r="R21">
+      <c r="S21">
         <v>0.121949501335621</v>
       </c>
-      <c r="S21">
+      <c r="T21">
         <v>24.1727477108113</v>
       </c>
-      <c r="T21">
+      <c r="U21">
         <v>79453490100.2467</v>
       </c>
-      <c r="U21">
+      <c r="V21">
         <v>0.965325264591292</v>
       </c>
-      <c r="V21">
+      <c r="W21">
         <v>55.004384033595</v>
       </c>
-      <c r="W21">
+      <c r="X21">
         <v>7.627</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:24">
       <c r="A22" s="1">
         <v>2010</v>
       </c>
@@ -1900,55 +1966,58 @@
         <v>54407453276.9085</v>
       </c>
       <c r="H22">
+        <v>2485482596184.71</v>
+      </c>
+      <c r="I22">
         <v>2.23331508815346</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>39598.957119545</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>33.7</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>21.529660508544</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>44.1378058416477</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>38.2669392926438</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>30.4160322973505</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>2.49265472467066</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>6.80033240372968</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>-6.62806882956297</v>
       </c>
-      <c r="R22">
+      <c r="S22">
         <v>0.411818206310272</v>
       </c>
-      <c r="S22">
+      <c r="T22">
         <v>25.2733978923915</v>
       </c>
-      <c r="T22">
+      <c r="U22">
         <v>98025460114.4247</v>
       </c>
-      <c r="U22">
+      <c r="V22">
         <v>1.13583836210976</v>
       </c>
-      <c r="V22">
+      <c r="W22">
         <v>59.2727749722888</v>
       </c>
-      <c r="W22">
+      <c r="X22">
         <v>7.924</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:24">
       <c r="A23" s="1">
         <v>2011</v>
       </c>
@@ -1971,55 +2040,58 @@
         <v>80833604086.8983</v>
       </c>
       <c r="H23">
+        <v>2663805834828.07</v>
+      </c>
+      <c r="I23">
         <v>1.13836239840663</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>42109.6418795749</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>33.2</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>20.8962522329618</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>42.7003650930175</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>33.5067575289157</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>32.1778069157158</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>3.85611244682819</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>7.75792611123319</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>-9.63532801231813</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <v>0.351707607507706</v>
       </c>
-      <c r="S23">
+      <c r="T23">
         <v>25.8349322442695</v>
       </c>
-      <c r="T23">
+      <c r="U23">
         <v>109733899591.288</v>
       </c>
-      <c r="U23">
+      <c r="V23">
         <v>1.11662614701046</v>
       </c>
-      <c r="V23">
+      <c r="W23">
         <v>63.5654009707745</v>
       </c>
-      <c r="W23">
+      <c r="X23">
         <v>8.169</v>
       </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:24">
       <c r="A24" s="1">
         <v>2012</v>
       </c>
@@ -2042,55 +2114,58 @@
         <v>12023540543.2668</v>
       </c>
       <c r="H24">
+        <v>2707089726614.64</v>
+      </c>
+      <c r="I24">
         <v>1.50899834668228</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>42490.1465463521</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>33.1</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>20.7376372383973</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>43.3321176508346</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>32.8653831004572</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>31.6074143016779</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>2.57323479654526</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>6.9182279834471</v>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <v>-9.91705155174577</v>
       </c>
-      <c r="R24">
+      <c r="S24">
         <v>0.40227073431015</v>
       </c>
-      <c r="S24">
+      <c r="T24">
         <v>25.1030655622434</v>
       </c>
-      <c r="T24">
+      <c r="U24">
         <v>117156976864.591</v>
       </c>
-      <c r="U24">
+      <c r="V24">
         <v>1.21181144741228</v>
       </c>
-      <c r="V24">
+      <c r="W24">
         <v>62.2259827334183</v>
       </c>
-      <c r="W24">
+      <c r="X24">
         <v>8.25</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:24">
       <c r="A25" s="1">
         <v>2013</v>
       </c>
@@ -2113,55 +2188,58 @@
         <v>46250908172.2106</v>
       </c>
       <c r="H25">
+        <v>2784853502534.29</v>
+      </c>
+      <c r="I25">
         <v>1.79992149702836</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>43419.0352598932</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>32.7</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>20.1291035337587</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>40.2043718258118</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>33.726066754577</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>31.7096871437064</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>2.29166666666667</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>7.33567444165963</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <v>-6.59501358792519</v>
       </c>
-      <c r="R25">
+      <c r="S25">
         <v>0.48620143532753</v>
       </c>
-      <c r="S25">
+      <c r="T25">
         <v>25.1363423809099</v>
       </c>
-      <c r="T25">
+      <c r="U25">
         <v>118750193779.676</v>
       </c>
-      <c r="U25">
+      <c r="V25">
         <v>1.19820109358142</v>
       </c>
-      <c r="V25">
+      <c r="W25">
         <v>61.9991119149908</v>
       </c>
-      <c r="W25">
+      <c r="X25">
         <v>7.704</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:24">
       <c r="A26" s="1">
         <v>2014</v>
       </c>
@@ -2184,55 +2262,58 @@
         <v>-113915346852.921</v>
       </c>
       <c r="H26">
+        <v>3064708247921.43</v>
+      </c>
+      <c r="I26">
         <v>3.19463731938923</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>47426.6209829995</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>33.1</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>19.8662130861835</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>39.4099587976251</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>32.8832964477046</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>30.518589390469</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>1.45112016293279</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>7.03254424971663</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <v>-6.88520999036786</v>
       </c>
-      <c r="R26">
+      <c r="S26">
         <v>0.415347635746002</v>
       </c>
-      <c r="S26">
+      <c r="T26">
         <v>24.8805109652867</v>
       </c>
-      <c r="T26">
+      <c r="U26">
         <v>124487425221.296</v>
       </c>
-      <c r="U26">
+      <c r="V26">
         <v>1.20982422016014</v>
       </c>
-      <c r="V26">
+      <c r="W26">
         <v>59.0948041195932</v>
       </c>
-      <c r="W26">
+      <c r="X26">
         <v>6.363</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:24">
       <c r="A27" s="1">
         <v>2015</v>
       </c>
@@ -2255,55 +2336,58 @@
         <v>-60177016430.4101</v>
       </c>
       <c r="H27">
+        <v>2927911140916.73</v>
+      </c>
+      <c r="I27">
         <v>2.22288842280334</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>44983.885522934</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>33.3</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>19.5485300693835</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>38.4439779571719</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>33.102489967132</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>29.3575990202724</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>0.36804684232537</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>6.29784461697161</v>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <v>-5.62080637595222</v>
       </c>
-      <c r="R27">
+      <c r="S27">
         <v>0.503706395626068</v>
       </c>
-      <c r="S27">
+      <c r="T27">
         <v>25.0666466296295</v>
       </c>
-      <c r="T27">
+      <c r="U27">
         <v>148109299505.898</v>
       </c>
-      <c r="U27">
+      <c r="V27">
         <v>1.56885775056848</v>
       </c>
-      <c r="V27">
+      <c r="W27">
         <v>57.2035496863734</v>
       </c>
-      <c r="W27">
+      <c r="X27">
         <v>5.517</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:24">
       <c r="A28" s="1">
         <v>2016</v>
       </c>
@@ -2326,55 +2410,58 @@
         <v>32908272028.5085</v>
       </c>
       <c r="H28">
+        <v>2689106566899.61</v>
+      </c>
+      <c r="I28">
         <v>1.92171009934007</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>40988.1044233026</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>33.1</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>19.21828438301</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>37.2555349974519</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>33.6041814680829</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>30.7980588910172</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>1.00841736811403</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>6.80338761020919</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <v>-3.81353102586053</v>
       </c>
-      <c r="R28">
+      <c r="S28">
         <v>0.347932636737823</v>
       </c>
-      <c r="S28">
+      <c r="T28">
         <v>25.4550384230121</v>
       </c>
-      <c r="T28">
+      <c r="U28">
         <v>134931850848.279</v>
       </c>
-      <c r="U28">
+      <c r="V28">
         <v>1.49593733402752</v>
       </c>
-      <c r="V28">
+      <c r="W28">
         <v>59.7003984143761</v>
       </c>
-      <c r="W28">
+      <c r="X28">
         <v>4.867</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:24">
       <c r="A29" s="1">
         <v>2017</v>
       </c>
@@ -2397,55 +2484,58 @@
         <v>172043885461.576</v>
       </c>
       <c r="H29">
+        <v>2680148052335.3</v>
+      </c>
+      <c r="I29">
         <v>2.65650487566202</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>40629.2340347345</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>32.6</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>18.6593209449109</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>37.1041862546711</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>33.9963082514039</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>32.2312989980226</v>
       </c>
-      <c r="O29">
+      <c r="P29">
         <v>2.55775577557753</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>7.48490982129915</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <v>-3.44752079489763</v>
       </c>
-      <c r="R29">
+      <c r="S29">
         <v>0.380680292844772</v>
       </c>
-      <c r="S29">
+      <c r="T29">
         <v>25.5968599008299</v>
       </c>
-      <c r="T29">
+      <c r="U29">
         <v>150857673778.943</v>
       </c>
-      <c r="U29">
+      <c r="V29">
         <v>1.58905823431859</v>
       </c>
-      <c r="V29">
+      <c r="W29">
         <v>63.1216500310687</v>
       </c>
-      <c r="W29">
+      <c r="X29">
         <v>4.452</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:24">
       <c r="A30" s="1">
         <v>2018</v>
       </c>
@@ -2468,55 +2558,58 @@
         <v>-28632134257.1304</v>
       </c>
       <c r="H30">
+        <v>2871340347581.79</v>
+      </c>
+      <c r="I30">
         <v>1.40519025981538</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>43315.4874501318</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>33.7</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>18.5412934232339</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>37.5296891145489</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>33.9609553297304</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>32.9625368906995</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>2.29283990345937</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>6.84045741705695</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>-3.89568573956095</v>
       </c>
-      <c r="R30">
+      <c r="S30">
         <v>0.0770855620503426</v>
       </c>
-      <c r="S30">
+      <c r="T30">
         <v>25.5467164489775</v>
       </c>
-      <c r="T30">
+      <c r="U30">
         <v>172657749536.315</v>
       </c>
-      <c r="U30">
+      <c r="V30">
         <v>1.62160065704145</v>
       </c>
-      <c r="V30">
+      <c r="W30">
         <v>64.542648250433</v>
       </c>
-      <c r="W30">
+      <c r="X30">
         <v>4.12</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:24">
       <c r="A31" s="1">
         <v>2019</v>
       </c>
@@ -2539,55 +2632,58 @@
         <v>-21498303884.1216</v>
       </c>
       <c r="H31">
+        <v>2851407164907.81</v>
+      </c>
+      <c r="I31">
         <v>1.62447518038404</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>42794.0022648288</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>32.8</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>19.0961094864142</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>36.7161596135226</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>33.5328778412486</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>33.0303533562736</v>
       </c>
-      <c r="O31">
+      <c r="P31">
         <v>1.73810460086515</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>6.16122700284074</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <v>-3.58862287430934</v>
       </c>
-      <c r="R31">
+      <c r="S31">
         <v>0.526694297790527</v>
       </c>
-      <c r="S31">
+      <c r="T31">
         <v>25.1112729590706</v>
       </c>
-      <c r="T31">
+      <c r="U31">
         <v>173569199262.767</v>
       </c>
-      <c r="U31">
+      <c r="V31">
         <v>1.68473544806755</v>
       </c>
-      <c r="V31">
+      <c r="W31">
         <v>64.66513363722351</v>
       </c>
-      <c r="W31">
+      <c r="X31">
         <v>3.613</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:24">
       <c r="A32" s="1">
         <v>2020</v>
       </c>
@@ -2610,55 +2706,58 @@
         <v>16388422616.9056</v>
       </c>
       <c r="H32">
+        <v>2696778386607.65</v>
+      </c>
+      <c r="I32">
         <v>-10.296918859171</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>40404.8062238951</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>32.6</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>22.6109420267119</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>48.0124897432167</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>33.7372818264538</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>29.1113418392136</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>0.989486703772449</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>4.29611381315252</v>
       </c>
-      <c r="Q32">
+      <c r="R32">
         <v>-14.9603087446268</v>
       </c>
-      <c r="R32">
+      <c r="S32">
         <v>0.483050256967545</v>
       </c>
-      <c r="S32">
+      <c r="T32">
         <v>24.7854276187243</v>
       </c>
-      <c r="T32">
+      <c r="U32">
         <v>180054101389.553</v>
       </c>
-      <c r="U32">
+      <c r="V32">
         <v>2.1161105409397</v>
       </c>
-      <c r="V32">
+      <c r="W32">
         <v>58.7811375973028</v>
       </c>
-      <c r="W32">
+      <c r="X32">
         <v>4.472</v>
       </c>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:24">
       <c r="A33" s="1">
         <v>2021</v>
       </c>
@@ -2681,55 +2780,58 @@
         <v>160748502105.858</v>
       </c>
       <c r="H33">
+        <v>3143323050707.26</v>
+      </c>
+      <c r="I33">
         <v>8.575950873930241</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>46926.475736105</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>32.4</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>22.259385665529</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>43.6472827513783</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>35.1040518071235</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>29.4042618360024</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>2.5183710961421</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>6.3537891660777</v>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <v>-9.338015227093731</v>
       </c>
-      <c r="R33">
+      <c r="S33">
         <v>0.489994138479233</v>
       </c>
-      <c r="S33">
+      <c r="T33">
         <v>26.4149383040168</v>
       </c>
-      <c r="T33">
+      <c r="U33">
         <v>194181397315.03</v>
       </c>
-      <c r="U33">
+      <c r="V33">
         <v>1.94383624666929</v>
       </c>
-      <c r="V33">
+      <c r="W33">
         <v>58.5845366237858</v>
       </c>
-      <c r="W33">
+      <c r="X33">
         <v>4.826</v>
       </c>
     </row>
-    <row r="34" spans="1:23">
+    <row r="34" spans="1:24">
       <c r="A34" s="1">
         <v>2022</v>
       </c>
@@ -2752,52 +2854,55 @@
         <v>124889342360.981</v>
       </c>
       <c r="H34">
+        <v>3114042471144.39</v>
+      </c>
+      <c r="I34">
         <v>4.83908517877134</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>46062.9914079698</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>20.8275082448421</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>41.5283554488788</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>36.680918672529</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>35.3133356660075</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>7.92204883147907</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>10.4413525177662</v>
       </c>
-      <c r="Q34">
+      <c r="R34">
         <v>-5.67306885452505</v>
       </c>
-      <c r="R34">
+      <c r="S34">
         <v>0.533176064491272</v>
       </c>
-      <c r="S34">
+      <c r="T34">
         <v>27.173147226044</v>
       </c>
-      <c r="T34">
+      <c r="U34">
         <v>176409966646.608</v>
       </c>
-      <c r="U34">
+      <c r="V34">
         <v>1.47611913760731</v>
       </c>
-      <c r="V34">
+      <c r="W34">
         <v>68.8805301397863</v>
       </c>
-      <c r="W34">
+      <c r="X34">
         <v>3.73</v>
       </c>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:24">
       <c r="A35" s="1">
         <v>2023</v>
       </c>
@@ -2820,52 +2925,55 @@
         <v>30207401209.3072</v>
       </c>
       <c r="H35">
+        <v>3369861888972.88</v>
+      </c>
+      <c r="I35">
         <v>0.39708234553963</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>49200.8101526146</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>20.5473252470783</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>41.8524003341712</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>35.9632042815227</v>
       </c>
-      <c r="N35">
+      <c r="O35">
         <v>33.0529270411278</v>
       </c>
-      <c r="O35">
+      <c r="P35">
         <v>6.79396706793964</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
         <v>7.76093332487292</v>
       </c>
-      <c r="Q35">
+      <c r="R35">
         <v>-6.85895650794763</v>
       </c>
-      <c r="R35">
+      <c r="S35">
         <v>0.5149356722831731</v>
       </c>
-      <c r="S35">
+      <c r="T35">
         <v>27.4079784300961</v>
       </c>
-      <c r="T35">
+      <c r="U35">
         <v>177915356242.234</v>
       </c>
-      <c r="U35">
+      <c r="V35">
         <v>1.26678417556899</v>
       </c>
-      <c r="V35">
+      <c r="W35">
         <v>65.0323382579942</v>
       </c>
-      <c r="W35">
+      <c r="X35">
         <v>3.984</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:24">
       <c r="A36" s="1">
         <v>2024</v>
       </c>
@@ -2882,27 +2990,30 @@
         <v>68306255487.3043</v>
       </c>
       <c r="H36">
+        <v>3643834188782.91</v>
+      </c>
+      <c r="I36">
         <v>1.10066786639271</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>52636.7865943853</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>31.7697823457053</v>
       </c>
-      <c r="O36">
+      <c r="P36">
         <v>3.27157294635921</v>
       </c>
-      <c r="T36">
+      <c r="U36">
         <v>174597843325.182</v>
       </c>
-      <c r="U36">
+      <c r="V36">
         <v>1.2208295060769</v>
       </c>
-      <c r="V36">
+      <c r="W36">
         <v>62.4075013968837</v>
       </c>
-      <c r="W36">
+      <c r="X36">
         <v>4.111</v>
       </c>
     </row>
